--- a/Config/MiniTemplate/Datas/reddot.xlsx
+++ b/Config/MiniTemplate/Datas/reddot.xlsx
@@ -4,19 +4,85 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
+  <si>
+    <t>##var</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>path</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>RedDotType</t>
+  </si>
+  <si>
+    <t>##group</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
+    <t>红点路径</t>
+  </si>
+  <si>
+    <t>红点名称</t>
+  </si>
+  <si>
+    <t>Main</t>
+  </si>
+  <si>
+    <t>0/1</t>
+  </si>
+  <si>
+    <t>RedDotTest</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -941,9 +1007,85 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="3"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4">
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4">
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/Config/MiniTemplate/Datas/reddot.xlsx
+++ b/Config/MiniTemplate/Datas/reddot.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
   <si>
     <t>##var</t>
   </si>
@@ -40,7 +40,7 @@
     <t>path</t>
   </si>
   <si>
-    <t>name</t>
+    <t>type</t>
   </si>
   <si>
     <t>##type</t>
@@ -70,13 +70,31 @@
     <t>红点名称</t>
   </si>
   <si>
-    <t>Main</t>
+    <t>Root</t>
   </si>
   <si>
     <t>0/1</t>
   </si>
   <si>
-    <t>RedDotTest</t>
+    <t>RedDotTest1</t>
+  </si>
+  <si>
+    <t>0/2</t>
+  </si>
+  <si>
+    <t>RedDotTest2</t>
+  </si>
+  <si>
+    <t>0/1/1</t>
+  </si>
+  <si>
+    <t>RedDotTestChild1</t>
+  </si>
+  <si>
+    <t>0/1/2</t>
+  </si>
+  <si>
+    <t>RedDotTestChild2</t>
   </si>
 </sst>
 </file>
@@ -692,8 +710,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1007,8 +1028,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="3"/>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="3" max="3" width="9.375" style="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
@@ -1017,7 +1041,7 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
@@ -1031,7 +1055,7 @@
       <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D2" t="s">
@@ -1045,7 +1069,7 @@
       <c r="B3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D3" t="s">
@@ -1056,7 +1080,7 @@
       <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D4" t="s">
@@ -1067,7 +1091,7 @@
       <c r="B5">
         <v>1</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>0</v>
       </c>
       <c r="D5" t="s">
@@ -1078,11 +1102,44 @@
       <c r="B6">
         <v>2</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D6" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4">
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4">
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4">
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
